--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487545_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487545_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.832</v>
+        <v>2.2078</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5178</v>
+        <v>6.9203</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.6858</v>
+        <v>-4.7125</v>
       </c>
       <c r="G2" t="n">
         <v>3.192</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5985</v>
+        <v>-0.0257</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3723</v>
+        <v>-0.2253</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2263</v>
+        <v>0.1995</v>
       </c>
       <c r="V2" t="n">
         <v>0.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1523</v>
+        <v>0.6047</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8805</v>
+        <v>2.5735</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7282</v>
+        <v>-1.9688</v>
       </c>
       <c r="G3" t="n">
         <v>0.6392</v>
@@ -688,13 +688,13 @@
         <v>0.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8253</v>
+        <v>0.2777</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2088</v>
+        <v>-0.5158</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0341</v>
+        <v>0.7935</v>
       </c>
       <c r="V3" t="n">
         <v>0.2754</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1792</v>
+        <v>0.0515</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7624</v>
+        <v>-0.703</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9416</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>-1.1554</v>
@@ -766,13 +766,13 @@
         <v>0.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0005</v>
+        <v>-0.1272</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0098</v>
+        <v>-0.9504</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0104</v>
+        <v>0.8232</v>
       </c>
       <c r="V4" t="n">
         <v>0.5507</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7713</v>
+        <v>-0.369</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4809</v>
+        <v>-0.3191</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2905</v>
+        <v>-0.0499</v>
       </c>
       <c r="G5" t="n">
         <v>-1.3763</v>
@@ -844,13 +844,13 @@
         <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.1678</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6534</v>
+        <v>-0.4917</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0833</v>
+        <v>0.3239</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9053</v>
+        <v>-0.8504</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3407</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.246</v>
+        <v>-1.3529</v>
       </c>
       <c r="G6" t="n">
         <v>-2.0685</v>
@@ -922,13 +922,13 @@
         <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0119</v>
+        <v>0.0429</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8316</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8197</v>
+        <v>0.7128</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1013</v>
+        <v>-1.0151</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6016</v>
+        <v>-0.5422</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4997</v>
+        <v>-0.473</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1367</v>
@@ -1000,13 +1000,13 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1604</v>
+        <v>-0.0743</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4752</v>
+        <v>-0.4158</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3148</v>
+        <v>0.3416</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0213</v>
+        <v>-1.8817</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6397</v>
+        <v>-1.5803</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3816</v>
+        <v>-0.3014</v>
       </c>
       <c r="G8" t="n">
         <v>-1.7864</v>
@@ -1078,13 +1078,13 @@
         <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3559</v>
+        <v>-0.2163</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6534</v>
+        <v>-0.594</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2975</v>
+        <v>0.3777</v>
       </c>
       <c r="V8" t="n">
         <v>1.492</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2899</v>
+        <v>-2.8225</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5118</v>
+        <v>-0.2048</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7782</v>
+        <v>-2.6178</v>
       </c>
       <c r="G9" t="n">
         <v>-4.6657</v>
@@ -1156,13 +1156,13 @@
         <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6829</v>
+        <v>-0.2156</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5764</v>
+        <v>-0.2694</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1066</v>
+        <v>0.0538</v>
       </c>
       <c r="V9" t="n">
         <v>0.8837</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.751</v>
+        <v>-3.7602</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5349</v>
+        <v>-2.3302</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2161</v>
+        <v>-1.43</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7759</v>
@@ -1234,13 +1234,13 @@
         <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0421</v>
+        <v>0.0329</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5764</v>
+        <v>-0.3717</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6185</v>
+        <v>0.4046</v>
       </c>
       <c r="V10" t="n">
         <v>0.3329</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2235</v>
+        <v>-4.6387</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0262</v>
+        <v>-0.7621</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.1973</v>
+        <v>-3.8765</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0206</v>
@@ -1312,13 +1312,13 @@
         <v>0.5875</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0865</v>
+        <v>-0.5017</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2725</v>
+        <v>0.0482</v>
       </c>
       <c r="V11" t="n">
         <v>0.2754</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.085000000000001</v>
+        <v>-8.917400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3565</v>
+        <v>-5.1354</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7285</v>
+        <v>-3.782</v>
       </c>
       <c r="G12" t="n">
         <v>-7.2035</v>
@@ -1390,13 +1390,13 @@
         <v>1.7626</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4691</v>
+        <v>-0.3014</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0516</v>
+        <v>-0.8305</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5825</v>
+        <v>0.529</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2166</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.9851</v>
+        <v>-21.391</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.174999999999999</v>
+        <v>-1.580799999999999</v>
       </c>
       <c r="F13" t="n">
         <v>-19.8103</v>
@@ -1468,13 +1468,13 @@
         <v>9.792200000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8704</v>
+        <v>-1.2765</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.478300000000001</v>
+        <v>-5.8844</v>
       </c>
       <c r="U13" t="n">
-        <v>4.608000000000001</v>
+        <v>4.607799999999999</v>
       </c>
       <c r="V13" t="n">
         <v>3.201800000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>M. SOUTO PARRADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.401</v>
+        <v>11.4663</v>
       </c>
       <c r="E14" t="n">
-        <v>9.4718</v>
+        <v>9.751200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9293</v>
+        <v>1.7151</v>
       </c>
       <c r="G14" t="n">
-        <v>9.011799999999999</v>
+        <v>8.3409</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6874</v>
+        <v>6.421</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3244</v>
+        <v>1.9199</v>
       </c>
       <c r="J14" t="n">
-        <v>9.722300000000001</v>
+        <v>8.787800000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7969</v>
+        <v>6.0752</v>
       </c>
       <c r="L14" t="n">
-        <v>6.9254</v>
+        <v>2.7126</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7105</v>
+        <v>-0.4469</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8905</v>
+        <v>0.3458</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.601</v>
+        <v>-0.7927</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9585</v>
+        <v>0.7834</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9585</v>
+        <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>1.039</v>
+        <v>0.1842</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2506</v>
+        <v>-0.4905</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2896</v>
+        <v>0.6747</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6083</v>
+        <v>2.1578</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6083</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SOUTO PARRADO</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7243</v>
+        <v>11.0166</v>
       </c>
       <c r="E15" t="n">
-        <v>9.5466</v>
+        <v>9.1647</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1777</v>
+        <v>1.8519</v>
       </c>
       <c r="G15" t="n">
-        <v>8.3409</v>
+        <v>9.011799999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>6.421</v>
+        <v>3.6874</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9199</v>
+        <v>5.3244</v>
       </c>
       <c r="J15" t="n">
-        <v>8.787800000000001</v>
+        <v>9.722300000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>6.0752</v>
+        <v>2.7969</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7126</v>
+        <v>6.9254</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4469</v>
+        <v>-0.7105</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3458</v>
+        <v>0.8905</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7927</v>
+        <v>-1.601</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7834</v>
+        <v>1.9585</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5578</v>
+        <v>0.6546</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6952</v>
+        <v>-0.5576</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1373</v>
+        <v>1.2122</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1578</v>
+        <v>-0.6083</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2754</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2676</v>
+        <v>4.861</v>
       </c>
       <c r="E16" t="n">
-        <v>4.8963</v>
+        <v>4.4869</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3713</v>
+        <v>0.3741</v>
       </c>
       <c r="G16" t="n">
         <v>3.7676</v>
@@ -1702,13 +1702,13 @@
         <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0507</v>
+        <v>0.6442</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1653</v>
+        <v>-0.2441</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8854</v>
+        <v>0.8882</v>
       </c>
       <c r="V16" t="n">
         <v>0.0576</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7954</v>
+        <v>3.3549</v>
       </c>
       <c r="E17" t="n">
-        <v>2.201</v>
+        <v>2.3033</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5944</v>
+        <v>1.0516</v>
       </c>
       <c r="G17" t="n">
         <v>3.739</v>
@@ -1780,13 +1780,13 @@
         <v>1.5668</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.0076</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6358</v>
+        <v>-0.5334</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0839</v>
+        <v>0.5411</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2838</v>
+        <v>1.5328</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0995</v>
+        <v>1.5088</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1844</v>
+        <v>0.024</v>
       </c>
       <c r="G18" t="n">
         <v>2.4468</v>
@@ -1858,13 +1858,13 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2495</v>
+        <v>0.4984</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.891</v>
+        <v>-0.4817</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1405</v>
+        <v>0.9801</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2166</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2133</v>
+        <v>1.2262</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0519</v>
+        <v>2.3589</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8386</v>
+        <v>-1.1326</v>
       </c>
       <c r="G19" t="n">
         <v>2.9131</v>
@@ -1936,13 +1936,13 @@
         <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1251</v>
+        <v>0.1381</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9504</v>
+        <v>-0.6434</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0755</v>
+        <v>0.7815</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8249</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0453</v>
+        <v>1.1522</v>
       </c>
       <c r="E20" t="n">
         <v>0.6407</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4046</v>
+        <v>0.5115</v>
       </c>
       <c r="G20" t="n">
         <v>1.0752</v>
@@ -2014,13 +2014,13 @@
         <v>0.1958</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2257</v>
+        <v>-0.1188</v>
       </c>
       <c r="T20" t="n">
         <v>-0.297</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0713</v>
+        <v>0.1782</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0343</v>
+        <v>-0.3301</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4868</v>
+        <v>-0.3844</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4525</v>
+        <v>0.0543</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6917</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9328</v>
+        <v>0.637</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.22</v>
+        <v>-0.1176</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1528</v>
+        <v>0.7546</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6372</v>
+        <v>-0.5837</v>
       </c>
       <c r="E22" t="n">
         <v>-0.9374</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3002</v>
+        <v>0.3537</v>
       </c>
       <c r="G22" t="n">
         <v>0.17</v>
@@ -2170,13 +2170,13 @@
         <v>0.1958</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0238</v>
+        <v>0.0297</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5121</v>
+        <v>-1.7656</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3501</v>
+        <v>-0.6571</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.162</v>
+        <v>-1.1086</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2653</v>
@@ -2248,13 +2248,13 @@
         <v>0.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3615</v>
+        <v>0.1079</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0306</v>
+        <v>-0.3376</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3921</v>
+        <v>0.4455</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>J. DOMINGUEZ FRAIZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7498</v>
+        <v>-4.4472</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0088</v>
+        <v>-4.1096</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7409</v>
+        <v>-0.3376</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.4115</v>
+        <v>-3.7379</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4995</v>
+        <v>-0.231</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.911</v>
+        <v>-3.5068</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1386</v>
+        <v>-3.4826</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4287</v>
+        <v>-0.2331</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.5673</v>
+        <v>-3.2495</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2729</v>
+        <v>-0.2552</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0708</v>
+        <v>0.0021</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3437</v>
+        <v>-0.2573</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1751</v>
+        <v>0.7834</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0.7834</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1122</v>
+        <v>-0.2761</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0882</v>
+        <v>-0.627</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0239</v>
+        <v>0.3508</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ FRAIZ</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8123</v>
+        <v>-4.8162</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3143</v>
+        <v>-4.3158</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.498</v>
+        <v>-0.5003</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.7379</v>
+        <v>-3.4115</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.231</v>
+        <v>0.4995</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.5068</v>
+        <v>-3.911</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.4826</v>
+        <v>-2.1386</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2331</v>
+        <v>0.4287</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.2495</v>
+        <v>-2.5673</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2552</v>
+        <v>-1.2729</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0021</v>
+        <v>0.0708</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2573</v>
+        <v>-1.3437</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7834</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R25" t="n">
         <v>0.7834</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6412</v>
+        <v>0.0457</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8316</v>
+        <v>-0.2188</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1904</v>
+        <v>0.2645</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>21.985</v>
+        <v>22.6672</v>
       </c>
       <c r="E26" t="n">
-        <v>19.8104</v>
+        <v>19.8102</v>
       </c>
       <c r="F26" t="n">
-        <v>2.1749</v>
+        <v>2.8571</v>
       </c>
       <c r="G26" t="n">
         <v>21.358</v>
@@ -2482,13 +2482,13 @@
         <v>11.7507</v>
       </c>
       <c r="S26" t="n">
-        <v>1.8704</v>
+        <v>2.5525</v>
       </c>
       <c r="T26" t="n">
         <v>-4.6081</v>
       </c>
       <c r="U26" t="n">
-        <v>6.4783</v>
+        <v>7.160500000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-3.2018</v>
